--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1298,13 +1298,13 @@
         <v>1000531424143</v>
       </c>
       <c r="K10" s="1">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="L10" s="2">
         <v>251913216895</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1796,7 +1796,7 @@
         <v>251913216895</v>
       </c>
       <c r="M22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1837,7 +1837,7 @@
         <v>251917518305</v>
       </c>
       <c r="M23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -2124,7 +2124,7 @@
         <v>251919159451</v>
       </c>
       <c r="M30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -2165,6 +2165,170 @@
         <v>251930308503</v>
       </c>
       <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C32">
+        <v>1018</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32">
+        <v>9500</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>500</v>
+      </c>
+      <c r="H32">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K32" s="1">
+        <v>46301</v>
+      </c>
+      <c r="L32" s="2">
+        <v>251917518305</v>
+      </c>
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C33">
+        <v>1012</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33">
+        <v>9500</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>500</v>
+      </c>
+      <c r="H33">
+        <v>10000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1000531424143</v>
+      </c>
+      <c r="K33" s="1">
+        <v>46282</v>
+      </c>
+      <c r="L33" s="2">
+        <v>251913216895</v>
+      </c>
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C34">
+        <v>1023</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>4750</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>250</v>
+      </c>
+      <c r="H34">
+        <v>5000</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J34" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K34" s="1">
+        <v>46296</v>
+      </c>
+      <c r="L34" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46282</v>
+      </c>
+      <c r="C35">
+        <v>1012</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35">
+        <v>85000</v>
+      </c>
+      <c r="F35">
+        <v>15</v>
+      </c>
+      <c r="G35">
+        <v>15000</v>
+      </c>
+      <c r="H35">
+        <v>100000</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1000531424143</v>
+      </c>
+      <c r="K35" s="1">
+        <v>46463</v>
+      </c>
+      <c r="L35" s="2">
+        <v>251913216895</v>
+      </c>
+      <c r="M35" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="EGSA2026_27_short_loan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1690,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="E20">
-        <v>21750</v>
+        <v>21250</v>
       </c>
       <c r="F20">
         <v>15</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -1222,7 +1222,7 @@
         <v>251912672957</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1667,7 +1667,7 @@
         <v>1000289318236</v>
       </c>
       <c r="K19" s="1">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="L19" s="2">
         <v>251926757080</v>
@@ -1749,7 +1749,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K21" s="1">
-        <v>46318</v>
+        <v>46289</v>
       </c>
       <c r="L21" s="2">
         <v>251912861288</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1667,13 +1667,13 @@
         <v>1000289318236</v>
       </c>
       <c r="K19" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="L19" s="2">
         <v>251926757080</v>
       </c>
       <c r="M19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -2329,6 +2329,47 @@
         <v>251913216895</v>
       </c>
       <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46287</v>
+      </c>
+      <c r="C36">
+        <v>1010</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36">
+        <v>13500</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>1500</v>
+      </c>
+      <c r="H36">
+        <v>15000</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K36" s="1">
+        <v>46317</v>
+      </c>
+      <c r="L36" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M36" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1749,13 +1749,13 @@
         <v>1000177190024</v>
       </c>
       <c r="K21" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="L21" s="2">
         <v>251912861288</v>
       </c>
       <c r="M21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -2159,13 +2159,13 @@
         <v>1000378957161</v>
       </c>
       <c r="K31" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="L31" s="2">
         <v>251930308503</v>
       </c>
       <c r="M31" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -2370,6 +2370,88 @@
         <v>251926757080</v>
       </c>
       <c r="M36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46288</v>
+      </c>
+      <c r="C37">
+        <v>1002</v>
+      </c>
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37">
+        <v>13500</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>1500</v>
+      </c>
+      <c r="H37">
+        <v>15000</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K37" s="1">
+        <v>46318</v>
+      </c>
+      <c r="L37" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46289</v>
+      </c>
+      <c r="C38">
+        <v>1014</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38">
+        <v>9500</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>500</v>
+      </c>
+      <c r="H38">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1000378957161</v>
+      </c>
+      <c r="K38" s="1">
+        <v>46309</v>
+      </c>
+      <c r="L38" s="2">
+        <v>251930308503</v>
+      </c>
+      <c r="M38" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2455,6 +2455,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46293</v>
+      </c>
+      <c r="C39">
+        <v>1002</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39">
+        <v>85000</v>
+      </c>
+      <c r="F39">
+        <v>15</v>
+      </c>
+      <c r="G39">
+        <v>15000</v>
+      </c>
+      <c r="H39">
+        <v>100000</v>
+      </c>
+      <c r="I39" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J39" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K39" s="1">
+        <v>46474</v>
+      </c>
+      <c r="L39" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1919,7 +1919,7 @@
         <v>251922956646</v>
       </c>
       <c r="M25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -1960,7 +1960,7 @@
         <v>251977677737</v>
       </c>
       <c r="M26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -2493,6 +2493,88 @@
         <v>251912861288</v>
       </c>
       <c r="M39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46294</v>
+      </c>
+      <c r="C40">
+        <v>1008</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40">
+        <v>13500</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>1500</v>
+      </c>
+      <c r="H40">
+        <v>15000</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J40" s="2">
+        <v>1000205376635</v>
+      </c>
+      <c r="K40" s="1">
+        <v>46324</v>
+      </c>
+      <c r="L40" s="2">
+        <v>251922956646</v>
+      </c>
+      <c r="M40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46294</v>
+      </c>
+      <c r="C41">
+        <v>1003</v>
+      </c>
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41">
+        <v>13500</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>1500</v>
+      </c>
+      <c r="H41">
+        <v>15000</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J41" s="2">
+        <v>1000496218101</v>
+      </c>
+      <c r="K41" s="1">
+        <v>46324</v>
+      </c>
+      <c r="L41" s="2">
+        <v>251977677737</v>
+      </c>
+      <c r="M41" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2288,7 +2288,7 @@
         <v>251919159451</v>
       </c>
       <c r="M34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -2575,6 +2575,47 @@
         <v>251977677737</v>
       </c>
       <c r="M41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46295</v>
+      </c>
+      <c r="C42">
+        <v>1023</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42">
+        <v>4750</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>250</v>
+      </c>
+      <c r="H42">
+        <v>5000</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J42" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K42" s="1">
+        <v>46310</v>
+      </c>
+      <c r="L42" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M42" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -2282,7 +2282,7 @@
         <v>1000657475649</v>
       </c>
       <c r="K34" s="1">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="L34" s="2">
         <v>251919159451</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2619,6 +2619,129 @@
         <v>14</v>
       </c>
     </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46296</v>
+      </c>
+      <c r="C43">
+        <v>1003</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43">
+        <v>85000</v>
+      </c>
+      <c r="F43">
+        <v>15</v>
+      </c>
+      <c r="G43">
+        <v>15000</v>
+      </c>
+      <c r="H43">
+        <v>100000</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1000496218101</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46478</v>
+      </c>
+      <c r="L43" s="2">
+        <v>251977677737</v>
+      </c>
+      <c r="M43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46296</v>
+      </c>
+      <c r="C44">
+        <v>1025</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44">
+        <v>21250</v>
+      </c>
+      <c r="F44">
+        <v>15</v>
+      </c>
+      <c r="G44">
+        <v>3750</v>
+      </c>
+      <c r="H44">
+        <v>25000</v>
+      </c>
+      <c r="I44" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J44" s="2">
+        <v>1000722471238</v>
+      </c>
+      <c r="K44" s="1">
+        <v>46357</v>
+      </c>
+      <c r="L44" s="2">
+        <v>251919408998</v>
+      </c>
+      <c r="M44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46296</v>
+      </c>
+      <c r="C45">
+        <v>1023</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45">
+        <v>21250</v>
+      </c>
+      <c r="F45">
+        <v>15</v>
+      </c>
+      <c r="G45">
+        <v>3750</v>
+      </c>
+      <c r="H45">
+        <v>25000</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K45" s="1">
+        <v>46357</v>
+      </c>
+      <c r="L45" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M45" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2742,6 +2742,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46296</v>
+      </c>
+      <c r="C46">
+        <v>1013</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46">
+        <v>21250</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="G46">
+        <v>3750</v>
+      </c>
+      <c r="H46">
+        <v>25000</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1000094217214</v>
+      </c>
+      <c r="K46" s="1">
+        <v>46357</v>
+      </c>
+      <c r="L46" s="2">
+        <v>251965224695</v>
+      </c>
+      <c r="M46" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1427,7 +1427,7 @@
         <v>251947763811</v>
       </c>
       <c r="M13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -2780,6 +2780,47 @@
         <v>251965224695</v>
       </c>
       <c r="M46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46297</v>
+      </c>
+      <c r="C47">
+        <v>1011</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47">
+        <v>21250</v>
+      </c>
+      <c r="F47">
+        <v>15</v>
+      </c>
+      <c r="G47">
+        <v>3750</v>
+      </c>
+      <c r="H47">
+        <v>25000</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J47" s="2">
+        <v>1000531405424</v>
+      </c>
+      <c r="K47" s="1">
+        <v>46359</v>
+      </c>
+      <c r="L47" s="2">
+        <v>251947763811</v>
+      </c>
+      <c r="M47" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2824,6 +2824,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C48">
+        <v>1011</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48">
+        <v>4750</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>250</v>
+      </c>
+      <c r="H48">
+        <v>5000</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J48" s="2">
+        <v>1000531405424</v>
+      </c>
+      <c r="K48" s="1">
+        <v>46315</v>
+      </c>
+      <c r="L48" s="2">
+        <v>251947763811</v>
+      </c>
+      <c r="M48" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,10 +887,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2865,6 +2866,88 @@
         <v>14</v>
       </c>
     </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C49">
+        <v>1005</v>
+      </c>
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49">
+        <v>13500</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49">
+        <v>1500</v>
+      </c>
+      <c r="H49">
+        <v>15000</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J49" s="2">
+        <v>1000263206022</v>
+      </c>
+      <c r="K49" s="1">
+        <v>46331</v>
+      </c>
+      <c r="L49" s="2">
+        <v>251935869198</v>
+      </c>
+      <c r="M49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46300</v>
+      </c>
+      <c r="C50">
+        <v>1018</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50">
+        <v>9500</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>500</v>
+      </c>
+      <c r="H50">
+        <v>10000</v>
+      </c>
+      <c r="I50" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J50" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K50" s="1">
+        <v>46320</v>
+      </c>
+      <c r="L50" s="2">
+        <v>251917518305</v>
+      </c>
+      <c r="M50" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -2201,13 +2201,13 @@
         <v>1066900097338</v>
       </c>
       <c r="K32" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="L32" s="2">
         <v>251917518305</v>
       </c>
       <c r="M32" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2948,6 +2948,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46302</v>
+      </c>
+      <c r="C51">
+        <v>1025</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51">
+        <v>9500</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51">
+        <v>500</v>
+      </c>
+      <c r="H51">
+        <v>10000</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1000722471238</v>
+      </c>
+      <c r="K51" s="1">
+        <v>46322</v>
+      </c>
+      <c r="L51" s="2">
+        <v>251919408998</v>
+      </c>
+      <c r="M51" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2989,6 +2989,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46304</v>
+      </c>
+      <c r="C52">
+        <v>1006</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52">
+        <v>85000</v>
+      </c>
+      <c r="F52">
+        <v>15</v>
+      </c>
+      <c r="G52">
+        <v>15000</v>
+      </c>
+      <c r="H52">
+        <v>100000</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J52" s="2">
+        <v>1000272980423</v>
+      </c>
+      <c r="K52" s="1">
+        <v>46486</v>
+      </c>
+      <c r="L52" s="2">
+        <v>251911818685</v>
+      </c>
+      <c r="M52" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -3030,6 +3030,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46305</v>
+      </c>
+      <c r="C53">
+        <v>1007</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53">
+        <v>4750</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53">
+        <v>250</v>
+      </c>
+      <c r="H53">
+        <v>5000</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J53" s="2">
+        <v>1000553520502</v>
+      </c>
+      <c r="K53" s="1">
+        <v>46320</v>
+      </c>
+      <c r="L53" s="2">
+        <v>251954846351</v>
+      </c>
+      <c r="M53" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1586,13 +1586,13 @@
         <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="L17" s="2">
         <v>251930308503</v>
       </c>
       <c r="M17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -2447,13 +2447,13 @@
         <v>1000378957161</v>
       </c>
       <c r="K38" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="L38" s="2">
         <v>251930308503</v>
       </c>
       <c r="M38" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -3068,6 +3068,47 @@
         <v>251954846351</v>
       </c>
       <c r="M53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <v>47405</v>
+      </c>
+      <c r="C54">
+        <v>1014</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54">
+        <v>9500</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>500</v>
+      </c>
+      <c r="H54">
+        <v>10000</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J54" s="2">
+        <v>1000378957161</v>
+      </c>
+      <c r="K54" s="1">
+        <v>46330</v>
+      </c>
+      <c r="L54" s="2">
+        <v>251930308503</v>
+      </c>
+      <c r="M54" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2611,13 +2611,13 @@
         <v>1000657475649</v>
       </c>
       <c r="K42" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="L42" s="2">
         <v>251919159451</v>
       </c>
       <c r="M42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
@@ -3076,7 +3076,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>47405</v>
+        <v>46309</v>
       </c>
       <c r="C54">
         <v>1014</v>
@@ -3109,6 +3109,47 @@
         <v>251930308503</v>
       </c>
       <c r="M54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46309</v>
+      </c>
+      <c r="C55">
+        <v>1023</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55">
+        <v>4750</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>250</v>
+      </c>
+      <c r="H55">
+        <v>5000</v>
+      </c>
+      <c r="I55" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J55" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K55" s="1">
+        <v>46325</v>
+      </c>
+      <c r="L55" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M55" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="21">
   <si>
     <t>loan_id</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>level_3</t>
+  </si>
+  <si>
+    <t>In Progres</t>
   </si>
 </sst>
 </file>
@@ -887,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1214,7 +1217,7 @@
         <v>1000724673337</v>
       </c>
       <c r="J8" s="2">
-        <v>10001490488816</v>
+        <v>1000490488816</v>
       </c>
       <c r="K8" s="1">
         <v>46285</v>
@@ -3151,6 +3154,88 @@
       </c>
       <c r="M55" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46311</v>
+      </c>
+      <c r="C56">
+        <v>1014</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56">
+        <v>21250</v>
+      </c>
+      <c r="F56">
+        <v>15</v>
+      </c>
+      <c r="G56">
+        <v>3750</v>
+      </c>
+      <c r="H56">
+        <v>25000</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1000378957161</v>
+      </c>
+      <c r="K56" s="1">
+        <v>46372</v>
+      </c>
+      <c r="L56" s="2">
+        <v>251930308503</v>
+      </c>
+      <c r="M56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46311</v>
+      </c>
+      <c r="C57">
+        <v>1001</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57">
+        <v>21250</v>
+      </c>
+      <c r="F57">
+        <v>15</v>
+      </c>
+      <c r="G57">
+        <v>3750</v>
+      </c>
+      <c r="H57">
+        <v>25000</v>
+      </c>
+      <c r="I57" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J57" s="2">
+        <v>1000490488816</v>
+      </c>
+      <c r="K57" s="1">
+        <v>46372</v>
+      </c>
+      <c r="L57" s="2">
+        <v>251912672957</v>
+      </c>
+      <c r="M57" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -2866,7 +2866,7 @@
         <v>251947763811</v>
       </c>
       <c r="M48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="21">
   <si>
     <t>loan_id</t>
   </si>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1712,13 +1712,13 @@
         <v>1000553520502</v>
       </c>
       <c r="K20" s="1">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="L20" s="2">
         <v>251954846351</v>
       </c>
       <c r="M20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -2368,13 +2368,13 @@
         <v>1000289318236</v>
       </c>
       <c r="K36" s="1">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="L36" s="2">
         <v>251926757080</v>
       </c>
       <c r="M36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -2409,13 +2409,13 @@
         <v>1000177190024</v>
       </c>
       <c r="K37" s="1">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="L37" s="2">
         <v>251912861288</v>
       </c>
       <c r="M37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -3235,6 +3235,129 @@
         <v>251912672957</v>
       </c>
       <c r="M57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C58">
+        <v>1010</v>
+      </c>
+      <c r="D58" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58">
+        <v>13500</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>1500</v>
+      </c>
+      <c r="H58">
+        <v>15000</v>
+      </c>
+      <c r="I58" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J58" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K58" s="1">
+        <v>46348</v>
+      </c>
+      <c r="L58" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C59">
+        <v>1002</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59">
+        <v>13500</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>1500</v>
+      </c>
+      <c r="H59">
+        <v>15000</v>
+      </c>
+      <c r="I59" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J59" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K59" s="1">
+        <v>46348</v>
+      </c>
+      <c r="L59" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M59" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46316</v>
+      </c>
+      <c r="C60">
+        <v>1007</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60">
+        <v>21250</v>
+      </c>
+      <c r="F60">
+        <v>15</v>
+      </c>
+      <c r="G60">
+        <v>3750</v>
+      </c>
+      <c r="H60">
+        <v>25000</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J60" s="2">
+        <v>1000553520502</v>
+      </c>
+      <c r="K60" s="1">
+        <v>46378</v>
+      </c>
+      <c r="L60" s="2">
+        <v>251954846351</v>
+      </c>
+      <c r="M60" t="s">
         <v>20</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="21">
   <si>
     <t>loan_id</t>
   </si>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2948,7 +2948,7 @@
         <v>251917518305</v>
       </c>
       <c r="M50" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -3065,13 +3065,13 @@
         <v>1000553520502</v>
       </c>
       <c r="K53" s="1">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="L53" s="2">
         <v>251954846351</v>
       </c>
       <c r="M53" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
@@ -3358,6 +3358,47 @@
         <v>251954846351</v>
       </c>
       <c r="M60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46318</v>
+      </c>
+      <c r="C61">
+        <v>1018</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61">
+        <v>9500</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>500</v>
+      </c>
+      <c r="H61">
+        <v>10000</v>
+      </c>
+      <c r="I61" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J61" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K61" s="1">
+        <v>46339</v>
+      </c>
+      <c r="L61" s="2">
+        <v>251917518305</v>
+      </c>
+      <c r="M61" t="s">
         <v>20</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -2942,7 +2942,7 @@
         <v>1066900097338</v>
       </c>
       <c r="K50" s="1">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="L50" s="2">
         <v>251917518305</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="22">
   <si>
     <t>loan_id</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>In Progres</t>
+  </si>
+  <si>
+    <t>In Progre</t>
   </si>
 </sst>
 </file>
@@ -890,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2983,13 +2986,13 @@
         <v>1000722471238</v>
       </c>
       <c r="K51" s="1">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="L51" s="2">
         <v>251919408998</v>
       </c>
       <c r="M51" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
@@ -3400,6 +3403,88 @@
       </c>
       <c r="M61" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46321</v>
+      </c>
+      <c r="C62">
+        <v>1011</v>
+      </c>
+      <c r="D62" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62">
+        <v>13500</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
+        <v>1500</v>
+      </c>
+      <c r="H62">
+        <v>15000</v>
+      </c>
+      <c r="I62" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J62" s="2">
+        <v>1000531405424</v>
+      </c>
+      <c r="K62" s="1">
+        <v>46352</v>
+      </c>
+      <c r="L62" s="2">
+        <v>251947763811</v>
+      </c>
+      <c r="M62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46321</v>
+      </c>
+      <c r="C63">
+        <v>1025</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63">
+        <v>9500</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>500</v>
+      </c>
+      <c r="H63">
+        <v>10000</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J63" s="2">
+        <v>1000378957161</v>
+      </c>
+      <c r="K63" s="1">
+        <v>46342</v>
+      </c>
+      <c r="L63" s="2">
+        <v>251919408998</v>
+      </c>
+      <c r="M63" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -1885,7 +1885,7 @@
         <v>251935869198</v>
       </c>
       <c r="M24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2535,13 +2535,13 @@
         <v>1000205376635</v>
       </c>
       <c r="K40" s="1">
-        <v>46324</v>
+        <v>46322</v>
       </c>
       <c r="L40" s="2">
         <v>251922956646</v>
       </c>
       <c r="M40" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -2576,13 +2576,13 @@
         <v>1000496218101</v>
       </c>
       <c r="K41" s="1">
-        <v>46324</v>
+        <v>46322</v>
       </c>
       <c r="L41" s="2">
         <v>251977677737</v>
       </c>
       <c r="M41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -2904,13 +2904,13 @@
         <v>1000263206022</v>
       </c>
       <c r="K49" s="1">
-        <v>46331</v>
+        <v>46322</v>
       </c>
       <c r="L49" s="2">
         <v>251935869198</v>
       </c>
       <c r="M49" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -79,12 +79,6 @@
   </si>
   <si>
     <t>level_3</t>
-  </si>
-  <si>
-    <t>In Progres</t>
-  </si>
-  <si>
-    <t>In Progre</t>
   </si>
 </sst>
 </file>
@@ -893,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -902,6 +896,7 @@
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2043,13 +2038,13 @@
         <v>1000016351087</v>
       </c>
       <c r="K28" s="1">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="L28" s="2">
         <v>251912356447</v>
       </c>
       <c r="M28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -3197,7 +3192,7 @@
         <v>251930308503</v>
       </c>
       <c r="M56" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
@@ -3238,7 +3233,7 @@
         <v>251912672957</v>
       </c>
       <c r="M57" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
@@ -3279,7 +3274,7 @@
         <v>251926757080</v>
       </c>
       <c r="M58" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
@@ -3320,7 +3315,7 @@
         <v>251912861288</v>
       </c>
       <c r="M59" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
@@ -3361,7 +3356,7 @@
         <v>251954846351</v>
       </c>
       <c r="M60" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
@@ -3402,7 +3397,7 @@
         <v>251917518305</v>
       </c>
       <c r="M61" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
@@ -3443,7 +3438,7 @@
         <v>251947763811</v>
       </c>
       <c r="M62" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
@@ -3484,7 +3479,48 @@
         <v>251919408998</v>
       </c>
       <c r="M63" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46324</v>
+      </c>
+      <c r="C64">
+        <v>1017</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64">
+        <v>21250</v>
+      </c>
+      <c r="F64">
+        <v>15</v>
+      </c>
+      <c r="G64">
+        <v>3750</v>
+      </c>
+      <c r="H64">
+        <v>25000</v>
+      </c>
+      <c r="I64" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J64" s="2">
+        <v>1000016351087</v>
+      </c>
+      <c r="K64" s="1">
+        <v>46386</v>
+      </c>
+      <c r="L64" s="2">
+        <v>251912356447</v>
+      </c>
+      <c r="M64" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2003,7 +2003,7 @@
         <v>251902666362</v>
       </c>
       <c r="M27" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -3521,6 +3521,44 @@
       </c>
       <c r="M64" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46325</v>
+      </c>
+      <c r="C65">
+        <v>1020</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65">
+        <v>21250</v>
+      </c>
+      <c r="F65">
+        <v>15</v>
+      </c>
+      <c r="G65">
+        <v>3750</v>
+      </c>
+      <c r="H65">
+        <v>25000</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J65" s="2">
+        <v>1000016981088</v>
+      </c>
+      <c r="K65" s="1">
+        <v>46386</v>
+      </c>
+      <c r="L65" s="2">
+        <v>251902666362</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2079,13 +2079,13 @@
         <v>1000548538797</v>
       </c>
       <c r="K29" s="1">
-        <v>46327</v>
+        <v>46325</v>
       </c>
       <c r="L29" s="2">
         <v>251965224695</v>
       </c>
       <c r="M29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -3151,7 +3151,7 @@
         <v>251919159451</v>
       </c>
       <c r="M55" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -3523,7 +3523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3559,6 +3559,91 @@
       </c>
       <c r="L65" s="2">
         <v>251902666362</v>
+      </c>
+      <c r="M65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46325</v>
+      </c>
+      <c r="C66">
+        <v>1023</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66">
+        <v>4750</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>250</v>
+      </c>
+      <c r="H66">
+        <v>5000</v>
+      </c>
+      <c r="I66" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J66" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K66" s="1">
+        <v>46341</v>
+      </c>
+      <c r="L66" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46325</v>
+      </c>
+      <c r="C67">
+        <v>1026</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67">
+        <v>21250</v>
+      </c>
+      <c r="F67">
+        <v>15</v>
+      </c>
+      <c r="G67">
+        <v>3750</v>
+      </c>
+      <c r="H67">
+        <v>25000</v>
+      </c>
+      <c r="I67" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J67" s="2">
+        <v>1000548538797</v>
+      </c>
+      <c r="K67" s="1">
+        <v>46386</v>
+      </c>
+      <c r="L67" s="2">
+        <v>251965224695</v>
+      </c>
+      <c r="M67" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
